--- a/test/generator/baseline/gen.tex.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.tex.to.xlsx.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Tables 4" sheetId="4" r:id="rId4"/>
     <sheet name="Tables 5" sheetId="5" r:id="rId5"/>
     <sheet name="Text" sheetId="6" r:id="rId6"/>
+    <sheet name="Notes" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -325,8 +326,10 @@
       <c r="C3">
         <v>103</v>
       </c>
-      <c r="D3">
-        <v>7</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+7</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -364,8 +367,10 @@
       <c r="C6">
         <v>20</v>
       </c>
-      <c r="D6">
-        <v>4</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+4</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1183,4 +1188,39 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="120" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Footnote 1</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In paged media, footnotes are usually displayed at the bottom of the text. However, in ebooks, a better paradigm is to make them clickable endnotes that the user can browse at her pleasure. This conversion is handled automatically by calibre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Endnote 1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Endnotes are typically used for longer notes, they remain endnotes when converted into ebook form, except that they have an additional backlink to make it easy to return to the current position after reading the note.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/test/generator/baseline/gen.tex.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.tex.to.xlsx.xlsx
@@ -804,7 +804,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Footnotes and endnotes are automatically recognized and both are converted to endnotes, with backlinks for maximum ease of use in ebook devices.</t>
+          <t xml:space="preserve">Footnotes [Footnote 1] and endnotes [Endnote 1] are automatically recognized and both are converted to endnotes, with backlinks for maximum ease of use in ebook devices.</t>
         </is>
       </c>
     </row>
@@ -1021,14 +1021,14 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">One</t>
+          <t xml:space="preserve">• One</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two</t>
+          <t xml:space="preserve">• Two</t>
         </is>
       </c>
     </row>
@@ -1042,14 +1042,14 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">One, with a very long line to demonstrate that the hanging indent for the list is working correctly</t>
+          <t xml:space="preserve">1. One, with a very long line to demonstrate that the hanging indent for the list is working correctly</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two</t>
+          <t xml:space="preserve">2. Two</t>
         </is>
       </c>
     </row>
@@ -1063,42 +1063,42 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">One</t>
+          <t xml:space="preserve">1. One</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two</t>
+          <t xml:space="preserve">1. Two</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Three</t>
+          <t xml:space="preserve">1. Three</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Four with a very long line to demonstrate that the hanging indent for the list is working correctly.</t>
+          <t xml:space="preserve">2. Four with a very long line to demonstrate that the hanging indent for the list is working correctly.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Five</t>
+          <t xml:space="preserve">3. Five</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Six</t>
+          <t xml:space="preserve">2. Six</t>
         </is>
       </c>
     </row>
@@ -1112,35 +1112,35 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">One</t>
+          <t xml:space="preserve">• One</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two</t>
+          <t xml:space="preserve">• Two</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">This bullet uses an image as the bullet item</t>
+          <t xml:space="preserve">• This bullet uses an image as the bullet item</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Four</t>
+          <t xml:space="preserve">• Four</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Five</t>
+          <t xml:space="preserve">• Five</t>
         </is>
       </c>
     </row>
@@ -1154,14 +1154,14 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">One</t>
+          <t xml:space="preserve">1. One</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two</t>
+          <t xml:space="preserve">2. Two</t>
         </is>
       </c>
     </row>
@@ -1175,14 +1175,14 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">We now resume our normal programming</t>
+          <t xml:space="preserve">3. We now resume our normal programming</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Four</t>
+          <t xml:space="preserve">4. Four</t>
         </is>
       </c>
     </row>

--- a/test/generator/baseline/gen.tex.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.tex.to.xlsx.xlsx
@@ -1187,6 +1187,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A30" r:id="rId1"/>
+  </hyperlinks>
 </worksheet>
 </file>
 

--- a/test/generator/baseline/gen.tex.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.tex.to.xlsx.xlsx
@@ -450,7 +450,6 @@
     <col min="10" max="10" width="8" customWidth="1"/>
     <col min="11" max="11" width="8" customWidth="1"/>
     <col min="12" max="12" width="8" customWidth="1"/>
-    <col min="13" max="13" width="8" customWidth="1"/>
     <col min="14" max="14" width="8" customWidth="1"/>
   </cols>
   <sheetData>
